--- a/input/carinfo-tests.xlsx
+++ b/input/carinfo-tests.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="43">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -49,7 +49,7 @@
     <t>The plate is entered</t>
   </si>
   <si>
-    <t>Click the Search button</t>
+    <t>Press Enter</t>
   </si>
   <si>
     <t>The lookup is submitted</t>
@@ -71,6 +71,12 @@
   </si>
   <si>
     <t>The heading names the plate</t>
+  </si>
+  <si>
+    <t>Verify that the vehicle title contains "XC40"</t>
+  </si>
+  <si>
+    <t>The heading names the model</t>
   </si>
   <si>
     <t>TC-CI-002</t>
@@ -514,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -645,44 +651,44 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
+      <c r="E8" t="s">
         <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
         <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
@@ -696,10 +702,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
         <v>7</v>
@@ -713,47 +719,47 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
         <v>28</v>
       </c>
-      <c r="B12" t="s">
+      <c r="E12" t="s">
         <v>29</v>
-      </c>
-      <c r="C12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
         <v>33</v>
@@ -764,87 +770,104 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
         <v>35</v>
       </c>
-      <c r="B15" t="s">
+      <c r="E15" t="s">
         <v>36</v>
-      </c>
-      <c r="C15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
         <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" t="s">
         <v>35</v>
       </c>
-      <c r="B19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" t="s">
-        <v>40</v>
+      <c r="E20" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/input/carinfo-tests.xlsx
+++ b/input/carinfo-tests.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="54">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -31,6 +31,39 @@
     <t>TC-CI-001</t>
   </si>
   <si>
+    <t>Open CarInfo site and create account</t>
+  </si>
+  <si>
+    <t>User has internet access</t>
+  </si>
+  <si>
+    <t>Open https://car.info/</t>
+  </si>
+  <si>
+    <t>click on login</t>
+  </si>
+  <si>
+    <t>Select Google</t>
+  </si>
+  <si>
+    <t>Enter username as karthikkmdec89@gmail.com</t>
+  </si>
+  <si>
+    <t>and password as Test@123</t>
+  </si>
+  <si>
+    <t>further requests for access, click on Continue</t>
+  </si>
+  <si>
+    <t>requests to Approve term of use , then select Confirm the terms of use and for user selection select Regular user and agree</t>
+  </si>
+  <si>
+    <t>In the search tab in the top, type KFG40L and search</t>
+  </si>
+  <si>
+    <t>TC-CI-005</t>
+  </si>
+  <si>
     <t>Look up a vehicle by registration number</t>
   </si>
   <si>
@@ -58,7 +91,7 @@
     <t>Verify that the vehicle page is displayed</t>
   </si>
   <si>
-    <t>The URL contains /search</t>
+    <t>The URL contains ?s=</t>
   </si>
   <si>
     <t>Verify that vehicle details are displayed</t>
@@ -520,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -547,7 +580,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -560,11 +593,8 @@
       <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -575,13 +605,10 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -592,13 +619,10 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -609,13 +633,10 @@
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -626,13 +647,10 @@
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -643,13 +661,10 @@
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -660,214 +675,344 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
         <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" t="s">
         <v>22</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
         <v>23</v>
       </c>
-      <c r="C12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" t="s">
-        <v>28</v>
-      </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" t="s">
         <v>30</v>
-      </c>
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E18" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" t="s">
         <v>37</v>
       </c>
-      <c r="B19" t="s">
+      <c r="E19" t="s">
         <v>38</v>
-      </c>
-      <c r="C19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" t="s">
-        <v>40</v>
-      </c>
-      <c r="E19" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" t="s">
         <v>42</v>
+      </c>
+      <c r="C21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" t="s">
+        <v>50</v>
+      </c>
+      <c r="E25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/input/carinfo-tests.xlsx
+++ b/input/carinfo-tests.xlsx
@@ -46,10 +46,10 @@
     <t>Select Google</t>
   </si>
   <si>
-    <t>Enter username as karthikkmdec89@gmail.com</t>
-  </si>
-  <si>
-    <t>and password as Test@123</t>
+    <t>Enter username as "&lt;username&gt;"</t>
+  </si>
+  <si>
+    <t>and password as "&lt;password&gt;"</t>
   </si>
   <si>
     <t>further requests for access, click on Continue</t>
